--- a/data/trans_dic/P16A_n_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,57 +717,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,68</t>
+          <t>0,15; 1,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,5</t>
+          <t>0,16; 1,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,57</t>
+          <t>0,06; 0,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,4</t>
+          <t>0,14; 1,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,81</t>
+          <t>0,08; 0,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,16</t>
+          <t>0,14; 1,32</t>
         </is>
       </c>
     </row>
@@ -1002,47 +1002,47 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,89</t>
+          <t>0,26; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,66</t>
+          <t>0,45; 2,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,84</t>
+          <t>0,31; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,78</t>
+          <t>0,82; 2,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,52</t>
+          <t>0,85; 2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,17</t>
+          <t>0,3; 1,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,85</t>
+          <t>0,69; 1,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,3</t>
+          <t>0,86; 2,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,38</t>
+          <t>0,34; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,4</t>
+          <t>0,34; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,08</t>
+          <t>0,92; 4,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,48</t>
+          <t>1,0; 3,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,18</t>
+          <t>1,57; 4,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,49</t>
+          <t>1,61; 4,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,52</t>
+          <t>4,44; 8,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,45</t>
+          <t>0,81; 2,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,74</t>
+          <t>1,19; 2,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,29</t>
+          <t>0,91; 2,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,45</t>
+          <t>2,45; 5,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,76</t>
+          <t>0,72; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,52</t>
+          <t>0,24; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,52</t>
+          <t>1,38; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,13</t>
+          <t>4,35; 8,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,52</t>
+          <t>3,22; 7,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,44</t>
+          <t>4,57; 9,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 9,36</t>
+          <t>4,47; 9,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,06</t>
+          <t>9,15; 13,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,93</t>
+          <t>2,18; 4,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,3</t>
+          <t>2,72; 5,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,32</t>
+          <t>3,36; 6,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,04</t>
+          <t>7,24; 9,92</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,59</t>
+          <t>2,18; 6,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,48</t>
+          <t>2,68; 8,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,32</t>
+          <t>3,86; 9,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,32</t>
+          <t>8,41; 13,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,23</t>
+          <t>4,6; 9,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 16,94</t>
+          <t>9,45; 17,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,69</t>
+          <t>8,21; 14,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 19,22</t>
+          <t>5,13; 19,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,73</t>
+          <t>3,91; 7,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,67</t>
+          <t>6,92; 11,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,02</t>
+          <t>6,78; 10,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 15,41</t>
+          <t>5,93; 15,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 14,72</t>
+          <t>6,04; 14,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,77</t>
+          <t>7,03; 16,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 11,86</t>
+          <t>5,78; 11,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 22,45</t>
+          <t>15,0; 22,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,46</t>
+          <t>4,83; 10,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,14; 22,36</t>
+          <t>13,8; 21,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,91; 18,46</t>
+          <t>10,75; 18,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,5; 35,79</t>
+          <t>29,73; 36,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,02</t>
+          <t>5,99; 10,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 18,1</t>
+          <t>12,33; 18,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 14,55</t>
+          <t>9,61; 14,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,7; 29,72</t>
+          <t>24,66; 29,55</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,97</t>
+          <t>1,12; 1,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,35</t>
+          <t>1,36; 2,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,09</t>
+          <t>1,25; 2,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,31</t>
+          <t>3,54; 5,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,2</t>
+          <t>2,11; 3,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,77</t>
+          <t>4,28; 5,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,04</t>
+          <t>3,67; 5,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,81</t>
+          <t>7,17; 9,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,42</t>
+          <t>1,71; 2,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,88</t>
+          <t>3,01; 3,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,46</t>
+          <t>2,62; 3,49</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,48</t>
+          <t>5,79; 7,44</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4754</t>
+          <t>0; 4675</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5665</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7044</t>
+          <t>0; 7950</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7974</t>
+          <t>0; 8892</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5665</t>
+          <t>0; 5722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7150</t>
+          <t>0; 7066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9830</t>
+          <t>0; 9864</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4410</t>
+          <t>0; 4202</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11930</t>
+          <t>0; 14267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5563</t>
+          <t>0; 5311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8506</t>
+          <t>0; 8473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6288</t>
+          <t>0; 6389</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>887; 10245</t>
+          <t>896; 10130</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>905; 8471</t>
+          <t>910; 7562</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7131</t>
+          <t>0; 7757</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>868; 7725</t>
+          <t>854; 7193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2526; 18172</t>
+          <t>1879; 16985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>961; 9383</t>
+          <t>966; 8623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1239; 10823</t>
+          <t>1282; 12333</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>867; 7126</t>
+          <t>865; 7127</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1054; 12899</t>
+          <t>1781; 12071</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2403; 14251</t>
+          <t>2406; 14798</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2890; 12671</t>
+          <t>2149; 12616</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5989; 19788</t>
+          <t>5831; 19087</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6596</t>
+          <t>0; 5825</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4837; 14928</t>
+          <t>5034; 15272</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3928; 15500</t>
+          <t>4007; 15991</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9488; 25826</t>
+          <t>9604; 26321</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6679</t>
+          <t>0; 6672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9524; 25953</t>
+          <t>9669; 24569</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1075; 12342</t>
+          <t>1776; 12203</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1967; 14741</t>
+          <t>2080; 15693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5418</t>
+          <t>0; 8129</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8740; 36218</t>
+          <t>8173; 37638</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5056; 17957</t>
+          <t>5134; 18296</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8661; 25746</t>
+          <t>9651; 26875</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11289; 29127</t>
+          <t>10469; 28543</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30613; 60756</t>
+          <t>31656; 59745</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8304; 25301</t>
+          <t>8337; 25118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14852; 33767</t>
+          <t>14612; 35669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11580; 29640</t>
+          <t>11800; 30293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38938; 87278</t>
+          <t>39179; 87459</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3246; 14537</t>
+          <t>2798; 13838</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1058; 10829</t>
+          <t>1043; 10680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6581; 21614</t>
+          <t>6582; 21627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25592; 45636</t>
+          <t>24423; 45636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12633; 30365</t>
+          <t>13022; 31056</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20686; 42251</t>
+          <t>20451; 41165</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22075; 46490</t>
+          <t>22222; 45160</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49652; 71532</t>
+          <t>50119; 71873</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18322; 38998</t>
+          <t>17227; 38308</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24216; 46465</t>
+          <t>23879; 46916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32994; 61645</t>
+          <t>32730; 59952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>80631; 111311</t>
+          <t>80263; 109995</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6495; 19272</t>
+          <t>6364; 18913</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8365; 26272</t>
+          <t>8297; 26031</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13310; 31153</t>
+          <t>12899; 30457</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31184; 49057</t>
+          <t>30965; 49834</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16094; 35095</t>
+          <t>15776; 34063</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33450; 59981</t>
+          <t>33442; 61154</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30786; 55502</t>
+          <t>31013; 54998</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32025; 116946</t>
+          <t>31188; 117122</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26691; 49115</t>
+          <t>24873; 46132</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47047; 77493</t>
+          <t>45920; 76972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48154; 78456</t>
+          <t>48307; 77640</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62702; 150440</t>
+          <t>57916; 151453</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13197; 30901</t>
+          <t>12675; 29598</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18010; 39403</t>
+          <t>17557; 40642</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14338; 30472</t>
+          <t>14850; 30500</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42964; 63470</t>
+          <t>42423; 62516</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14995; 34922</t>
+          <t>16130; 36081</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55020; 86977</t>
+          <t>53665; 84939</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43652; 73856</t>
+          <t>42999; 73017</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125618; 152401</t>
+          <t>126605; 154560</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32652; 59906</t>
+          <t>32597; 59109</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78297; 115644</t>
+          <t>78754; 115814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61281; 95634</t>
+          <t>63168; 97518</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>174995; 210567</t>
+          <t>174737; 209368</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36592; 64528</t>
+          <t>36732; 62924</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>45861; 80691</t>
+          <t>46500; 81122</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43049; 70937</t>
+          <t>42439; 71332</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123430; 183887</t>
+          <t>122552; 181536</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>69379; 108246</t>
+          <t>71158; 107516</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>154178; 205263</t>
+          <t>152290; 203778</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>127474; 178651</t>
+          <t>130043; 183207</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>264499; 364092</t>
+          <t>266250; 365936</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>113981; 161115</t>
+          <t>113739; 160060</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>205742; 271287</t>
+          <t>210195; 272328</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>179161; 239935</t>
+          <t>181738; 242032</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>421523; 536767</t>
+          <t>415423; 533785</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,66</t>
+          <t>0,15; 1,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,53</t>
+          <t>0,06; 0,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,31</t>
+          <t>0,2; 1,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,75</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,12; 1,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,12</t>
+          <t>0,14; 1,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,77</t>
+          <t>0,16; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,76</t>
+          <t>0,38; 2,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,83</t>
+          <t>0,31; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,69</t>
+          <t>0,84; 2,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,58</t>
+          <t>1,03; 2,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,2</t>
+          <t>0,3; 1,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,89</t>
+          <t>0,64; 1,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,18</t>
+          <t>0,87; 2,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,35</t>
+          <t>0,21; 2,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,55</t>
+          <t>0,33; 2,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,24</t>
+          <t>2,18; 5,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,55</t>
+          <t>0,98; 3,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,36</t>
+          <t>1,56; 4,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,4</t>
+          <t>1,68; 4,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,38</t>
+          <t>4,18; 7,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,43</t>
+          <t>0,8; 2,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,9</t>
+          <t>1,11; 2,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,34</t>
+          <t>0,9; 2,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,46</t>
+          <t>3,56; 5,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,58</t>
+          <t>0,89; 3,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,49</t>
+          <t>0,24; 2,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,53</t>
+          <t>1,37; 4,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,13</t>
+          <t>4,24; 7,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,69</t>
+          <t>3,02; 7,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,19</t>
+          <t>4,46; 9,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,09</t>
+          <t>4,56; 9,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,15; 13,12</t>
+          <t>9,29; 13,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,84</t>
+          <t>2,22; 4,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,35</t>
+          <t>2,76; 5,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,15</t>
+          <t>3,39; 6,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,92</t>
+          <t>7,29; 10,12</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,46</t>
+          <t>2,12; 6,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,4</t>
+          <t>2,66; 8,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,11</t>
+          <t>3,85; 8,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,54</t>
+          <t>7,63; 12,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,93</t>
+          <t>4,72; 10,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 17,28</t>
+          <t>9,31; 16,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,56</t>
+          <t>7,93; 14,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 19,25</t>
+          <t>16,14; 21,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,26</t>
+          <t>3,95; 7,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,6</t>
+          <t>6,95; 11,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,9</t>
+          <t>6,74; 11,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,93; 15,51</t>
+          <t>12,91; 16,46</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 14,1</t>
+          <t>6,11; 14,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 16,27</t>
+          <t>7,35; 16,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,87</t>
+          <t>5,82; 12,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,0; 22,11</t>
+          <t>15,09; 22,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,81</t>
+          <t>4,67; 10,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,8; 21,84</t>
+          <t>14,12; 22,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 18,25</t>
+          <t>10,71; 18,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,73; 36,3</t>
+          <t>29,55; 35,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,87</t>
+          <t>6,12; 10,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,33; 18,13</t>
+          <t>12,02; 17,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,84</t>
+          <t>9,47; 14,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,66; 29,55</t>
+          <t>24,75; 29,45</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,92</t>
+          <t>1,12; 2,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,37</t>
+          <t>1,36; 2,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,1</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,25</t>
+          <t>4,15; 5,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,18</t>
+          <t>2,1; 3,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,73</t>
+          <t>4,26; 5,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,17</t>
+          <t>3,66; 5,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,86</t>
+          <t>8,86; 10,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,4</t>
+          <t>1,72; 2,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,9</t>
+          <t>3,0; 3,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,49</t>
+          <t>2,63; 3,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,44</t>
+          <t>6,72; 7,72</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4675</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>0; 4689</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7950</t>
+          <t>0; 7405</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,17 +2103,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8892</t>
+          <t>0; 10175</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5722</t>
+          <t>0; 6587</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7066</t>
+          <t>0; 7111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9864</t>
+          <t>0; 11862</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4534</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4202</t>
+          <t>0; 4402</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 14267</t>
+          <t>0; 13567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5311</t>
+          <t>0; 4854</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8473</t>
+          <t>0; 9027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6389</t>
+          <t>0; 6144</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>896; 10130</t>
+          <t>890; 10483</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>910; 7562</t>
+          <t>906; 7541</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7757</t>
+          <t>0; 6385</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>854; 7193</t>
+          <t>863; 8001</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1879; 16985</t>
+          <t>2556; 18915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>966; 8623</t>
+          <t>968; 9489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1282; 12333</t>
+          <t>1176; 10875</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>17328</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>865; 7127</t>
+          <t>876; 7192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1781; 12071</t>
+          <t>1063; 12956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2499,47 +2499,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2406; 14798</t>
+          <t>2332; 13946</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2149; 12616</t>
+          <t>2150; 12954</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5831; 19087</t>
+          <t>5943; 19141</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5825</t>
+          <t>0; 6122</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5034; 15272</t>
+          <t>6416; 17708</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4007; 15991</t>
+          <t>4037; 16230</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9604; 26321</t>
+          <t>8890; 24946</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6672</t>
+          <t>0; 6258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9669; 24569</t>
+          <t>10798; 26554</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>40522</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64304</t>
+          <t>63847</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1776; 12203</t>
+          <t>1086; 12061</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2080; 15693</t>
+          <t>2041; 14697</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8129</t>
+          <t>0; 5443</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8173; 37638</t>
+          <t>15279; 37016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5134; 18296</t>
+          <t>5076; 18499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9651; 26875</t>
+          <t>9627; 25135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10469; 28543</t>
+          <t>10893; 27942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31656; 59745</t>
+          <t>30801; 52039</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8337; 25118</t>
+          <t>8289; 23786</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14612; 35669</t>
+          <t>13719; 33289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11800; 30293</t>
+          <t>11661; 29925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39179; 87459</t>
+          <t>51173; 80882</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60250</t>
+          <t>67858</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94429</t>
+          <t>103991</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2798; 13838</t>
+          <t>3437; 15163</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1043; 10680</t>
+          <t>1051; 10009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6582; 21627</t>
+          <t>6544; 22100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24423; 45636</t>
+          <t>25824; 48373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13022; 31056</t>
+          <t>12203; 30045</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20451; 41165</t>
+          <t>19969; 40975</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22222; 45160</t>
+          <t>22636; 45648</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50119; 71873</t>
+          <t>56557; 81065</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17227; 38308</t>
+          <t>17527; 38336</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23879; 46916</t>
+          <t>24214; 46544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32730; 59952</t>
+          <t>33078; 59566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>80263; 109995</t>
+          <t>88841; 123231</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>40953</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>74281</t>
+          <t>81986</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>113825</t>
+          <t>122939</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6364; 18913</t>
+          <t>6191; 19062</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8297; 26031</t>
+          <t>8238; 26046</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12899; 30457</t>
+          <t>12856; 29164</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30965; 49834</t>
+          <t>31057; 49953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15776; 34063</t>
+          <t>16184; 34812</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33442; 61154</t>
+          <t>32961; 59078</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31013; 54998</t>
+          <t>29955; 55257</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31188; 117122</t>
+          <t>70885; 93414</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24873; 46132</t>
+          <t>25114; 48463</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45920; 76972</t>
+          <t>46116; 77187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48307; 77640</t>
+          <t>48000; 79165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57916; 151453</t>
+          <t>109237; 139311</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>58008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>139915</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>191954</t>
+          <t>209358</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12675; 29598</t>
+          <t>12816; 29723</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17557; 40642</t>
+          <t>18356; 42209</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14850; 30500</t>
+          <t>14952; 31065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42423; 62516</t>
+          <t>46819; 70519</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16130; 36081</t>
+          <t>15580; 34896</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53665; 84939</t>
+          <t>54917; 86636</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42999; 73017</t>
+          <t>42873; 75134</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>126605; 154560</t>
+          <t>137297; 165989</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32597; 59109</t>
+          <t>33273; 59517</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78754; 115814</t>
+          <t>76775; 113659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63168; 97518</t>
+          <t>62250; 96002</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>174737; 209368</t>
+          <t>191727; 228178</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>329805</t>
+          <t>356614</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>524028</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36732; 62924</t>
+          <t>36699; 66042</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>46500; 81122</t>
+          <t>46738; 84898</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42439; 71332</t>
+          <t>41897; 72025</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>122552; 181536</t>
+          <t>146648; 190405</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>71158; 107516</t>
+          <t>71073; 109134</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>152290; 203778</t>
+          <t>151751; 205189</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>130043; 183207</t>
+          <t>129772; 177696</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>266250; 365936</t>
+          <t>331277; 390470</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>113739; 160060</t>
+          <t>114323; 159065</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>210195; 272328</t>
+          <t>209642; 270618</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>181738; 242032</t>
+          <t>182546; 241787</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>415423; 533785</t>
+          <t>488369; 561122</t>
         </is>
       </c>
     </row>
